--- a/Commercial Vehicles Sales Revenue Dashboard with KPI Tracker_StudentName.xlsx.xlsx
+++ b/Commercial Vehicles Sales Revenue Dashboard with KPI Tracker_StudentName.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1ED5F73-6FAC-4ABA-81D7-D8707070AED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26B6811-C632-414C-9367-7DBE184A026C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A1A363EA-7E0A-486D-9E10-AE977EBDCBA2}"/>
   </bookViews>
@@ -108,9 +108,9 @@
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="\+0.00%;\-0.00%;0.00%"/>
-    <numFmt numFmtId="166" formatCode="&quot;₹&quot;#,##0.00&quot; Cr&quot;"/>
-    <numFmt numFmtId="169" formatCode="#,##0&quot; Units&quot;"/>
-    <numFmt numFmtId="170" formatCode="&quot;₹&quot;#,##0.00&quot; L&quot;"/>
+    <numFmt numFmtId="165" formatCode="&quot;₹&quot;#,##0.00&quot; Cr&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot; Units&quot;"/>
+    <numFmt numFmtId="167" formatCode="&quot;₹&quot;#,##0.00&quot; L&quot;"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -149,41 +149,41 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="28"/>
       <color theme="1"/>
       <name val="Gadugi"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="24"/>
+      <color rgb="FF0000FF"/>
+      <name val="Gadugi"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
       <color rgb="FFFFC000"/>
       <name val="Gadugi"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="24"/>
       <color theme="8" tint="0.39997558519241921"/>
       <name val="Gadugi"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="24"/>
       <color rgb="FFFF0000"/>
       <name val="Gadugi"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF0000FF"/>
-      <name val="Gadugi"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -205,6 +205,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -364,15 +370,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -388,11 +385,20 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -406,29 +412,29 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="10" fontId="7" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="10" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -437,91 +443,6 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="23">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <sz val="12"/>
-        <name val="Gadugi"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Gadugi"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Gadugi"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="&quot;₹&quot;#,##0.00&quot; L&quot;"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -566,37 +487,13 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Gadugi"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -604,135 +501,7 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Gadugi"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Gadugi"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Gadugi"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Gadugi"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
+        <top/>
         <bottom/>
       </border>
     </dxf>
@@ -783,7 +552,327 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="#,##0&quot; Units&quot;"/>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Gadugi"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Gadugi"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\+0.00%;\-0.00%;0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Gadugi"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Gadugi"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="&quot;₹&quot;#,##0.00&quot; Cr&quot;"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="double">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Gadugi"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Gadugi"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="&quot;₹&quot;#,##0.00&quot; Cr&quot;"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="double">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Gadugi"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Gadugi"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="&quot;₹&quot;#,##0.00&quot; L&quot;"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Gadugi"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Gadugi"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="#,##0&quot; Units&quot;"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -819,119 +908,16 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;#,##0.00&quot; Cr&quot;"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="double">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Gadugi"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;#,##0.00&quot; Cr&quot;"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="double">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Gadugi"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Gadugi"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\+0.00%;\-0.00%;0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -997,38 +983,64 @@
       <font>
         <b/>
         <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
+        <sz val="12"/>
         <name val="Gadugi"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </left>
         <right style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Gadugi"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
         <top/>
         <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Slicer Style 1" pivot="0" table="0" count="1" xr9:uid="{309E7A06-19D1-4E39-B1F0-DAE583035D25}">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="wholeTable" dxfId="22"/>
     </tableStyle>
     <tableStyle name="Slicer Style 2" pivot="0" table="0" count="1" xr9:uid="{5160BC73-104A-48B3-8190-8C15BBD1F55B}">
-      <tableStyleElement type="wholeTable" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="21"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -3189,7 +3201,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="en-IN"/>
               </a:p>
             </c:txPr>
           </c:dispUnitsLbl>
@@ -4193,7 +4205,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -7699,7 +7711,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="0" y="1645920"/>
+          <a:off x="0" y="2148840"/>
           <a:ext cx="19397980" cy="15179947"/>
           <a:chOff x="0" y="1577340"/>
           <a:chExt cx="19359880" cy="14543677"/>
@@ -7820,8 +7832,8 @@
           </a:graphicData>
         </a:graphic>
       </xdr:graphicFrame>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+        <mc:Choice Requires="sle15">
           <xdr:graphicFrame macro="">
             <xdr:nvGraphicFramePr>
               <xdr:cNvPr id="9" name="OEM / Brand">
@@ -7844,7 +7856,7 @@
             </a:graphic>
           </xdr:graphicFrame>
         </mc:Choice>
-        <mc:Fallback>
+        <mc:Fallback xmlns="">
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
               <xdr:cNvPr id="0" name=""/>
@@ -7886,6 +7898,50 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>670560</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>677487</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92486BFE-87A1-A6AE-20B5-B060A26D1A7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2103120" cy="860367"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7906,16 +7962,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D353EA63-9005-4AB6-85B7-4CD7F85E9EEB}" name="Table1" displayName="Table1" ref="A1:G5" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D353EA63-9005-4AB6-85B7-4CD7F85E9EEB}" name="Table1" displayName="Table1" ref="A1:G5" headerRowDxfId="3" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A1:G5" xr:uid="{D353EA63-9005-4AB6-85B7-4CD7F85E9EEB}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{385ED653-00A2-430B-8536-624EBDD76A97}" name="OEM / Brand" totalsRowLabel="Total" dataDxfId="18" totalsRowDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{E1D63451-DB80-4645-868E-5D127AB0EF18}" name="Units of Commercial Vehicles Sold (July 2026)" dataDxfId="13" totalsRowDxfId="7" dataCellStyle="Comma"/>
-    <tableColumn id="3" xr3:uid="{46C69FA7-1A18-4D47-80C9-DD081D0B9938}" name="Avg. Selling Price (₹ Lakh / Unit)" dataDxfId="2" totalsRowDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{39C17DF8-DB59-44CB-A7E7-93DD7810AB48}" name="Total Revenue (₹ Cr)" dataDxfId="14" totalsRowDxfId="9" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{F55F29AB-9144-412E-A64A-166E61354EC4}" name="Target Revenue (₹ Cr)" dataDxfId="15" totalsRowDxfId="10" dataCellStyle="Comma"/>
-    <tableColumn id="6" xr3:uid="{EB964FFD-974F-4109-A581-1F8006A276E0}" name="Revenue Variance (%)" dataDxfId="17" totalsRowDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{DB05F903-4347-4A8F-9D97-FCFB1C66A3E2}" name="YoY Revenue Growth (%)" totalsRowFunction="sum" dataDxfId="16" totalsRowDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{385ED653-00A2-430B-8536-624EBDD76A97}" name="OEM / Brand" totalsRowLabel="Total" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{E1D63451-DB80-4645-868E-5D127AB0EF18}" name="Units of Commercial Vehicles Sold (July 2026)" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{46C69FA7-1A18-4D47-80C9-DD081D0B9938}" name="Avg. Selling Price (₹ Lakh / Unit)" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{39C17DF8-DB59-44CB-A7E7-93DD7810AB48}" name="Total Revenue (₹ Cr)" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{F55F29AB-9144-412E-A64A-166E61354EC4}" name="Target Revenue (₹ Cr)" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{EB964FFD-974F-4109-A581-1F8006A276E0}" name="Revenue Variance (%)" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{DB05F903-4347-4A8F-9D97-FCFB1C66A3E2}" name="YoY Revenue Growth (%)" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8251,26 +8307,26 @@
     <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="27" t="s">
         <v>5</v>
       </c>
     </row>
@@ -8278,22 +8334,22 @@
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="12">
         <v>39641</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="13">
         <v>18.5</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="11">
         <v>7333.59</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="11">
         <v>7100</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="7">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="8">
         <v>0.36899999999999999</v>
       </c>
     </row>
@@ -8301,22 +8357,22 @@
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="12">
         <v>19590</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="13">
         <v>21</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="11">
         <v>4113.8999999999996</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="11">
         <v>4250</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="7">
         <v>-3.2000000000000001E-2</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="8">
         <v>0.3</v>
       </c>
     </row>
@@ -8324,45 +8380,45 @@
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="12">
         <v>8241</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="13">
         <v>16.2</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="11">
         <v>1335.04</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="11">
         <v>1300</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="7">
         <v>2.69E-2</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="8">
         <v>0.158</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="12">
         <v>1667</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="14">
         <v>28.5</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="11">
         <v>475.1</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="11">
         <v>450</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="9">
         <v>5.5800000000000002E-2</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="10">
         <v>0.14199999999999999</v>
       </c>
     </row>
@@ -8370,19 +8426,19 @@
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="12">
         <f>SUM(B2:B5)</f>
         <v>69139</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="15">
         <f>(D6*100)/B6</f>
         <v>19.175327962510305</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="11">
         <f>SUM(D2:D5)</f>
         <v>13257.63</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="11">
         <f>SUM(E2:E5)</f>
         <v>13100</v>
       </c>
@@ -8398,13 +8454,13 @@
     <row r="7" spans="1:7" ht="14.4" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="F2:F5">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8447,7 +8503,7 @@
       <c r="G1" s="16"/>
       <c r="H1" s="16"/>
     </row>
-    <row r="2" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -8458,94 +8514,94 @@
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="17" t="s">
+      <c r="B3" s="17"/>
+      <c r="C3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="18" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="19" t="s">
+      <c r="F3" s="19"/>
+      <c r="G3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="19"/>
+      <c r="H3" s="20"/>
     </row>
     <row r="4" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
     </row>
     <row r="5" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
     </row>
     <row r="6" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24">
+      <c r="A7" s="21">
         <f>Data_Master!D6</f>
         <v>13257.63</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="20">
+      <c r="B7" s="21"/>
+      <c r="C7" s="22">
         <f>Data_Master!F6</f>
         <v>1.2032824427480856E-2</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="21">
+      <c r="D7" s="22"/>
+      <c r="E7" s="23">
         <f>Data_Master!B6</f>
         <v>69139</v>
       </c>
-      <c r="F7" s="21"/>
-      <c r="G7" s="22">
+      <c r="F7" s="23"/>
+      <c r="G7" s="24">
         <f>Data_Master!G6</f>
         <v>0.24225000000000002</v>
       </c>
-      <c r="H7" s="22"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/Commercial Vehicles Sales Revenue Dashboard with KPI Tracker_StudentName.xlsx.xlsx
+++ b/Commercial Vehicles Sales Revenue Dashboard with KPI Tracker_StudentName.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26B6811-C632-414C-9367-7DBE184A026C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642A9D88-70B3-4C6D-9F14-5E67DE430F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A1A363EA-7E0A-486D-9E10-AE977EBDCBA2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A1A363EA-7E0A-486D-9E10-AE977EBDCBA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Master" sheetId="1" r:id="rId1"/>
@@ -400,6 +400,27 @@
     <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -414,27 +435,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -469,41 +469,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Gadugi"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -977,6 +942,41 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Gadugi"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -7689,12 +7689,12 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>157534</xdr:colOff>
       <xdr:row>92</xdr:row>
       <xdr:rowOff>907</xdr:rowOff>
     </xdr:to>
@@ -7711,10 +7711,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="0" y="2148840"/>
-          <a:ext cx="19397980" cy="15179947"/>
-          <a:chOff x="0" y="1577340"/>
-          <a:chExt cx="19359880" cy="14543677"/>
+          <a:off x="0" y="883920"/>
+          <a:ext cx="23810014" cy="16444867"/>
+          <a:chOff x="0" y="365439"/>
+          <a:chExt cx="23763137" cy="15755578"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:graphicFrame macro="">
@@ -7832,8 +7832,8 @@
           </a:graphicData>
         </a:graphic>
       </xdr:graphicFrame>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-        <mc:Choice Requires="sle15">
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
           <xdr:graphicFrame macro="">
             <xdr:nvGraphicFramePr>
               <xdr:cNvPr id="9" name="OEM / Brand">
@@ -7846,8 +7846,8 @@
               <xdr:cNvGraphicFramePr/>
             </xdr:nvGraphicFramePr>
             <xdr:xfrm>
-              <a:off x="9161143" y="1645920"/>
-              <a:ext cx="3079686" cy="1537547"/>
+              <a:off x="19347114" y="365439"/>
+              <a:ext cx="4416023" cy="2292390"/>
             </xdr:xfrm>
             <a:graphic>
               <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
@@ -7856,7 +7856,7 @@
             </a:graphic>
           </xdr:graphicFrame>
         </mc:Choice>
-        <mc:Fallback xmlns="">
+        <mc:Fallback>
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
               <xdr:cNvPr id="0" name=""/>
@@ -7866,8 +7866,8 @@
             </xdr:nvSpPr>
             <xdr:spPr>
               <a:xfrm>
-                <a:off x="9179172" y="1717500"/>
-                <a:ext cx="3085747" cy="1604813"/>
+                <a:off x="19385280" y="883920"/>
+                <a:ext cx="4424734" cy="2392680"/>
               </a:xfrm>
               <a:prstGeom prst="rect">
                 <a:avLst/>
@@ -7962,16 +7962,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D353EA63-9005-4AB6-85B7-4CD7F85E9EEB}" name="Table1" displayName="Table1" ref="A1:G5" headerRowDxfId="3" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D353EA63-9005-4AB6-85B7-4CD7F85E9EEB}" name="Table1" displayName="Table1" ref="A1:G5" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
   <autoFilter ref="A1:G5" xr:uid="{D353EA63-9005-4AB6-85B7-4CD7F85E9EEB}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{385ED653-00A2-430B-8536-624EBDD76A97}" name="OEM / Brand" totalsRowLabel="Total" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{E1D63451-DB80-4645-868E-5D127AB0EF18}" name="Units of Commercial Vehicles Sold (July 2026)" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Comma"/>
-    <tableColumn id="3" xr3:uid="{46C69FA7-1A18-4D47-80C9-DD081D0B9938}" name="Avg. Selling Price (₹ Lakh / Unit)" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{39C17DF8-DB59-44CB-A7E7-93DD7810AB48}" name="Total Revenue (₹ Cr)" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{F55F29AB-9144-412E-A64A-166E61354EC4}" name="Target Revenue (₹ Cr)" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Comma"/>
-    <tableColumn id="6" xr3:uid="{EB964FFD-974F-4109-A581-1F8006A276E0}" name="Revenue Variance (%)" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{DB05F903-4347-4A8F-9D97-FCFB1C66A3E2}" name="YoY Revenue Growth (%)" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{385ED653-00A2-430B-8536-624EBDD76A97}" name="OEM / Brand" totalsRowLabel="Total" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{E1D63451-DB80-4645-868E-5D127AB0EF18}" name="Units of Commercial Vehicles Sold (July 2026)" dataDxfId="14" totalsRowDxfId="13" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{46C69FA7-1A18-4D47-80C9-DD081D0B9938}" name="Avg. Selling Price (₹ Lakh / Unit)" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{39C17DF8-DB59-44CB-A7E7-93DD7810AB48}" name="Total Revenue (₹ Cr)" dataDxfId="10" totalsRowDxfId="9" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{F55F29AB-9144-412E-A64A-166E61354EC4}" name="Target Revenue (₹ Cr)" dataDxfId="8" totalsRowDxfId="7" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{EB964FFD-974F-4109-A581-1F8006A276E0}" name="Revenue Variance (%)" dataDxfId="6" totalsRowDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{DB05F903-4347-4A8F-9D97-FCFB1C66A3E2}" name="YoY Revenue Growth (%)" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8308,25 +8308,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="18" t="s">
         <v>5</v>
       </c>
     </row>
@@ -8492,116 +8492,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18" t="s">
+      <c r="B3" s="24"/>
+      <c r="C3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="19" t="s">
+      <c r="D3" s="25"/>
+      <c r="E3" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="20" t="s">
+      <c r="F3" s="26"/>
+      <c r="G3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="20"/>
+      <c r="H3" s="27"/>
     </row>
     <row r="4" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
     </row>
     <row r="5" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
     </row>
     <row r="6" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21">
+      <c r="A7" s="19">
         <f>Data_Master!D6</f>
         <v>13257.63</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="22">
+      <c r="B7" s="19"/>
+      <c r="C7" s="20">
         <f>Data_Master!F6</f>
         <v>1.2032824427480856E-2</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23">
+      <c r="D7" s="20"/>
+      <c r="E7" s="21">
         <f>Data_Master!B6</f>
         <v>69139</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="24">
+      <c r="F7" s="21"/>
+      <c r="G7" s="22">
         <f>Data_Master!G6</f>
         <v>0.24225000000000002</v>
       </c>
-      <c r="H7" s="24"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="9">
